--- a/ISMS/PGDM FY ( TREAM 1)/business analysis/CLG source and practice/teaching.xlsx
+++ b/ISMS/PGDM FY ( TREAM 1)/business analysis/CLG source and practice/teaching.xlsx
@@ -2,20 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\OneDrive\Documents\Obsidian Vault\ISMS\PGDM FY ( TREAM 1)\business analysis\CLG source and practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8974BA9F-8ADB-4895-B85E-10A35DF14109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB4B6E7-B9C9-4F49-BC9E-B1126FE5470C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="2" xr2:uid="{A02E834C-DC8B-4D5C-AC9A-B4F77F1604EC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="4" xr2:uid="{A02E834C-DC8B-4D5C-AC9A-B4F77F1604EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">Sheet1!$M$20:$P$23</definedName>
@@ -114,8 +116,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="64">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -247,13 +271,78 @@
   </si>
   <si>
     <t>Wast</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>Area A</t>
+  </si>
+  <si>
+    <t>Area B</t>
+  </si>
+  <si>
+    <t>%Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Cum sales </t>
+  </si>
+  <si>
+    <t>% sales</t>
+  </si>
+  <si>
+    <t>% cum sales</t>
+  </si>
+  <si>
+    <t>couse</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Sr NO</t>
+  </si>
+  <si>
+    <t>Sr no</t>
+  </si>
+  <si>
+    <t>pareto index</t>
+  </si>
+  <si>
+    <t>RETAILER</t>
+  </si>
+  <si>
+    <t>avrage</t>
+  </si>
+  <si>
+    <t>standerd deviation</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Z_score</t>
+  </si>
+  <si>
+    <t>sum</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>max</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="169" formatCode="0.00000"/>
+    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="174" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +363,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -348,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -381,6 +476,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -459,6 +561,1008 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent1">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent2">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent3">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent4">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent4">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="103000"/>
+                      <a:lumMod val="102000"/>
+                      <a:tint val="94000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent5">
+                      <a:satMod val="110000"/>
+                      <a:lumMod val="100000"/>
+                      <a:shade val="100000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="99000"/>
+                      <a:satMod val="120000"/>
+                      <a:shade val="78000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$D$15:$D$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$E$15:$E$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-54F4-4FFC-8C72-A80C4A5053D1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="344">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -527,7 +1631,7 @@
                   <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
                   <a:extLst>
                     <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                      <a14:cameraTool cellRange="$A$1:$E$7" spid="_x0000_s3096"/>
+                      <a14:cameraTool cellRange="$A$1:$E$7" spid="_x0000_s3117"/>
                     </a:ext>
                   </a:extLst>
                 </xdr:cNvPicPr>
@@ -576,7 +1680,7 @@
                   <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
                   <a:extLst>
                     <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                      <a14:cameraTool cellRange="$G$1:$K$7" spid="_x0000_s3097"/>
+                      <a14:cameraTool cellRange="$G$1:$K$7" spid="_x0000_s3118"/>
                     </a:ext>
                   </a:extLst>
                 </xdr:cNvPicPr>
@@ -626,7 +1730,7 @@
                 <a:picLocks noChangeArrowheads="1"/>
                 <a:extLst>
                   <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                    <a14:cameraTool cellRange="$A$11:$E$15" spid="_x0000_s3098"/>
+                    <a14:cameraTool cellRange="$A$11:$E$15" spid="_x0000_s3119"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPicPr>
@@ -668,6 +1772,47 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>265157</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>36555</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>280603</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>184836</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{468DB765-77B7-025E-BBC3-F10270085286}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2196,4 +3341,1043 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDC58810-CE5A-4982-BF3D-8A78C49FE96D}">
+  <dimension ref="A1:V19"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="6.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="8.88671875" style="13"/>
+    <col min="7" max="7" width="6.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="16.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3" style="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4" style="13" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="13.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="5" style="13" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="9.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="4" style="13" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="12.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="14.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="12.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="15.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="12.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="16.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="54" max="55" width="12.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="56" max="57" width="16.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="58" max="63" width="12.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="64" max="65" width="18.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="66" max="67" width="16.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="68" max="16384" width="8.88671875" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12">
+        <v>1578</v>
+      </c>
+      <c r="C2" s="12">
+        <v>3598</v>
+      </c>
+      <c r="G2" s="12">
+        <v>1</v>
+      </c>
+      <c r="H2" s="15">
+        <f>I2/$I$15</f>
+        <v>0.43736141906873616</v>
+      </c>
+      <c r="I2" s="12">
+        <v>1578</v>
+      </c>
+      <c r="J2" s="15">
+        <f>+H2</f>
+        <v>0.43736141906873616</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="12">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12">
+        <v>150</v>
+      </c>
+      <c r="C3" s="12">
+        <v>436</v>
+      </c>
+      <c r="G3" s="12">
+        <v>2</v>
+      </c>
+      <c r="H3" s="15">
+        <f>I3/$I$15</f>
+        <v>0.34922394678492241</v>
+      </c>
+      <c r="I3" s="12">
+        <v>1260</v>
+      </c>
+      <c r="J3" s="15">
+        <f>+J2+H3</f>
+        <v>0.78658536585365857</v>
+      </c>
+      <c r="O3" s="13">
+        <v>1</v>
+      </c>
+      <c r="P3" s="15">
+        <f>Q3/$Q$19</f>
+        <v>0.48536355051935787</v>
+      </c>
+      <c r="Q3" s="12">
+        <v>3598</v>
+      </c>
+      <c r="R3" s="15">
+        <f>+P3</f>
+        <v>0.48536355051935787</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12">
+        <v>89</v>
+      </c>
+      <c r="C4" s="12">
+        <v>141</v>
+      </c>
+      <c r="G4" s="12">
+        <v>3</v>
+      </c>
+      <c r="H4" s="15">
+        <f>I4/$I$15</f>
+        <v>4.1574279379157426E-2</v>
+      </c>
+      <c r="I4" s="12">
+        <v>150</v>
+      </c>
+      <c r="J4" s="15">
+        <f t="shared" ref="J4:J14" si="0">+J3+H4</f>
+        <v>0.82815964523281604</v>
+      </c>
+      <c r="O4" s="13">
+        <v>2</v>
+      </c>
+      <c r="P4" s="15">
+        <f t="shared" ref="P4:P18" si="1">Q4/$Q$19</f>
+        <v>0.16187778227438285</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>1200</v>
+      </c>
+      <c r="R4" s="15">
+        <f>+R3+P4</f>
+        <v>0.64724133279374074</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="12">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12">
+        <v>93</v>
+      </c>
+      <c r="C5" s="12">
+        <v>90</v>
+      </c>
+      <c r="G5" s="12">
+        <v>4</v>
+      </c>
+      <c r="H5" s="15">
+        <f>I5/$I$15</f>
+        <v>2.6330376940133036E-2</v>
+      </c>
+      <c r="I5" s="12">
+        <v>95</v>
+      </c>
+      <c r="J5" s="15">
+        <f t="shared" si="0"/>
+        <v>0.85449002217294912</v>
+      </c>
+      <c r="O5" s="13">
+        <v>3</v>
+      </c>
+      <c r="P5" s="15">
+        <f t="shared" si="1"/>
+        <v>5.8815594226359097E-2</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>436</v>
+      </c>
+      <c r="R5" s="15">
+        <f t="shared" ref="R5:R18" si="2">+R4+P5</f>
+        <v>0.70605692702009981</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12">
+        <v>91</v>
+      </c>
+      <c r="C6" s="12">
+        <v>40</v>
+      </c>
+      <c r="G6" s="12">
+        <v>5</v>
+      </c>
+      <c r="H6" s="15">
+        <f>I6/$I$15</f>
+        <v>2.5776053215077605E-2</v>
+      </c>
+      <c r="I6" s="12">
+        <v>93</v>
+      </c>
+      <c r="J6" s="15">
+        <f t="shared" si="0"/>
+        <v>0.8802660753880267</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="O6" s="13">
+        <v>4</v>
+      </c>
+      <c r="P6" s="15">
+        <f t="shared" si="1"/>
+        <v>5.3419668150546336E-2</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>396</v>
+      </c>
+      <c r="R6" s="15">
+        <f t="shared" si="2"/>
+        <v>0.75947659517064614</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12">
+        <v>43</v>
+      </c>
+      <c r="C7" s="12">
+        <v>45</v>
+      </c>
+      <c r="G7" s="12">
+        <v>6</v>
+      </c>
+      <c r="H7" s="15">
+        <f>I7/$I$15</f>
+        <v>2.5221729490022174E-2</v>
+      </c>
+      <c r="I7" s="12">
+        <v>91</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" si="0"/>
+        <v>0.90548780487804892</v>
+      </c>
+      <c r="K7" s="14">
+        <f>G3/G14</f>
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="L7" s="14">
+        <f>J3</f>
+        <v>0.78658536585365857</v>
+      </c>
+      <c r="O7" s="13">
+        <v>5</v>
+      </c>
+      <c r="P7" s="15">
+        <f t="shared" si="1"/>
+        <v>5.3419668150546336E-2</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>396</v>
+      </c>
+      <c r="R7" s="15">
+        <f t="shared" si="2"/>
+        <v>0.81289626332119247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12">
+        <v>1260</v>
+      </c>
+      <c r="C8" s="12">
+        <v>92</v>
+      </c>
+      <c r="G8" s="12">
+        <v>7</v>
+      </c>
+      <c r="H8" s="15">
+        <f>I8/$I$15</f>
+        <v>2.4667405764966739E-2</v>
+      </c>
+      <c r="I8" s="12">
+        <v>89</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" si="0"/>
+        <v>0.93015521064301565</v>
+      </c>
+      <c r="K8" s="12">
+        <v>1</v>
+      </c>
+      <c r="L8" s="14">
+        <f>L7/K7</f>
+        <v>5.11280487804878</v>
+      </c>
+      <c r="M8" s="14">
+        <f>L8+K8</f>
+        <v>6.11280487804878</v>
+      </c>
+      <c r="O8" s="13">
+        <v>6</v>
+      </c>
+      <c r="P8" s="15">
+        <f t="shared" si="1"/>
+        <v>4.1278834479967622E-2</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>306</v>
+      </c>
+      <c r="R8" s="15">
+        <f t="shared" si="2"/>
+        <v>0.85417509780116008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12">
+        <v>95</v>
+      </c>
+      <c r="C9" s="12">
+        <v>45</v>
+      </c>
+      <c r="G9" s="12">
+        <v>8</v>
+      </c>
+      <c r="H9" s="15">
+        <f>I9/$I$15</f>
+        <v>1.1917960088691795E-2</v>
+      </c>
+      <c r="I9" s="12">
+        <v>43</v>
+      </c>
+      <c r="J9" s="15">
+        <f t="shared" si="0"/>
+        <v>0.94207317073170749</v>
+      </c>
+      <c r="O9" s="13">
+        <v>7</v>
+      </c>
+      <c r="P9" s="15">
+        <f t="shared" si="1"/>
+        <v>4.1143936328072304E-2</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>305</v>
+      </c>
+      <c r="R9" s="15">
+        <f t="shared" si="2"/>
+        <v>0.89531903412923242</v>
+      </c>
+      <c r="T9" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="U9" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="V9" s="12"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12">
+        <v>42</v>
+      </c>
+      <c r="C10" s="12">
+        <v>305</v>
+      </c>
+      <c r="G10" s="12">
+        <v>9</v>
+      </c>
+      <c r="H10" s="15">
+        <f>I10/$I$15</f>
+        <v>1.1917960088691795E-2</v>
+      </c>
+      <c r="I10" s="12">
+        <v>43</v>
+      </c>
+      <c r="J10" s="15">
+        <f t="shared" si="0"/>
+        <v>0.95399113082039932</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" s="16">
+        <f>LOG(M8)/LOG(L8)</f>
+        <v>1.1094761943140337</v>
+      </c>
+      <c r="O10" s="13">
+        <v>8</v>
+      </c>
+      <c r="P10" s="15">
+        <f t="shared" si="1"/>
+        <v>2.0774315391879131E-2</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>154</v>
+      </c>
+      <c r="R10" s="15">
+        <f t="shared" si="2"/>
+        <v>0.91609334952111154</v>
+      </c>
+      <c r="T10" s="15">
+        <f>P6</f>
+        <v>5.3419668150546336E-2</v>
+      </c>
+      <c r="U10" s="15">
+        <f>R6</f>
+        <v>0.75947659517064614</v>
+      </c>
+      <c r="V10" s="12"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="12">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12">
+        <v>43</v>
+      </c>
+      <c r="C11" s="12">
+        <v>396</v>
+      </c>
+      <c r="G11" s="12">
+        <v>10</v>
+      </c>
+      <c r="H11" s="15">
+        <f>I11/$I$15</f>
+        <v>1.1917960088691795E-2</v>
+      </c>
+      <c r="I11" s="12">
+        <v>43</v>
+      </c>
+      <c r="J11" s="15">
+        <f t="shared" si="0"/>
+        <v>0.96590909090909116</v>
+      </c>
+      <c r="O11" s="13">
+        <v>9</v>
+      </c>
+      <c r="P11" s="15">
+        <f t="shared" si="1"/>
+        <v>1.9020639417239985E-2</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>141</v>
+      </c>
+      <c r="R11" s="15">
+        <f t="shared" si="2"/>
+        <v>0.93511398893835151</v>
+      </c>
+      <c r="T11" s="12">
+        <v>1</v>
+      </c>
+      <c r="U11" s="17">
+        <f>U10/T10</f>
+        <v>14.217171717171718</v>
+      </c>
+      <c r="V11" s="17">
+        <f>U11+T11</f>
+        <v>15.217171717171718</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12">
+        <v>39</v>
+      </c>
+      <c r="C12" s="12">
+        <v>1200</v>
+      </c>
+      <c r="G12" s="12">
+        <v>11</v>
+      </c>
+      <c r="H12" s="15">
+        <f>I12/$I$15</f>
+        <v>1.164079822616408E-2</v>
+      </c>
+      <c r="I12" s="12">
+        <v>42</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" si="0"/>
+        <v>0.9775498891352552</v>
+      </c>
+      <c r="O12" s="13">
+        <v>10</v>
+      </c>
+      <c r="P12" s="15">
+        <f t="shared" si="1"/>
+        <v>1.6727370835019559E-2</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>124</v>
+      </c>
+      <c r="R12" s="15">
+        <f t="shared" si="2"/>
+        <v>0.95184135977337103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12">
+        <v>42</v>
+      </c>
+      <c r="C13" s="12">
+        <v>396</v>
+      </c>
+      <c r="G13" s="12">
+        <v>12</v>
+      </c>
+      <c r="H13" s="15">
+        <f>I13/$I$15</f>
+        <v>1.164079822616408E-2</v>
+      </c>
+      <c r="I13" s="12">
+        <v>42</v>
+      </c>
+      <c r="J13" s="15">
+        <f t="shared" si="0"/>
+        <v>0.98919068736141924</v>
+      </c>
+      <c r="O13" s="13">
+        <v>11</v>
+      </c>
+      <c r="P13" s="15">
+        <f t="shared" si="1"/>
+        <v>1.2410629974369352E-2</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>92</v>
+      </c>
+      <c r="R13" s="15">
+        <f t="shared" si="2"/>
+        <v>0.9642519897477404</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <v>13</v>
+      </c>
+      <c r="B14" s="12">
+        <v>43</v>
+      </c>
+      <c r="C14" s="12">
+        <v>306</v>
+      </c>
+      <c r="G14" s="12">
+        <v>13</v>
+      </c>
+      <c r="H14" s="15">
+        <f>I14/$I$15</f>
+        <v>1.0809312638580931E-2</v>
+      </c>
+      <c r="I14" s="12">
+        <v>39</v>
+      </c>
+      <c r="J14" s="15">
+        <f>+J13+H14</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="O14" s="13">
+        <v>12</v>
+      </c>
+      <c r="P14" s="15">
+        <f t="shared" si="1"/>
+        <v>1.2140833670578713E-2</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>90</v>
+      </c>
+      <c r="R14" s="15">
+        <f t="shared" si="2"/>
+        <v>0.97639282341831912</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="12">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12">
+        <v>154</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12">
+        <f>SUM(I2:I14)</f>
+        <v>3608</v>
+      </c>
+      <c r="J15" s="12"/>
+      <c r="O15" s="13">
+        <v>13</v>
+      </c>
+      <c r="P15" s="15">
+        <f t="shared" si="1"/>
+        <v>6.0704168352893563E-3</v>
+      </c>
+      <c r="Q15" s="12">
+        <v>45</v>
+      </c>
+      <c r="R15" s="15">
+        <f t="shared" si="2"/>
+        <v>0.98246324025360843</v>
+      </c>
+      <c r="T15" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="U15" s="16">
+        <f>LOG(V11)/LOG(U11)</f>
+        <v>1.0256075591929579</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <v>15</v>
+      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12">
+        <v>124</v>
+      </c>
+      <c r="O16" s="13">
+        <v>14</v>
+      </c>
+      <c r="P16" s="15">
+        <f t="shared" si="1"/>
+        <v>6.0704168352893563E-3</v>
+      </c>
+      <c r="Q16" s="12">
+        <v>45</v>
+      </c>
+      <c r="R16" s="15">
+        <f t="shared" si="2"/>
+        <v>0.98853365708889773</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="12">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12">
+        <v>45</v>
+      </c>
+      <c r="O17" s="13">
+        <v>15</v>
+      </c>
+      <c r="P17" s="15">
+        <f t="shared" si="1"/>
+        <v>6.0704168352893563E-3</v>
+      </c>
+      <c r="Q17" s="12">
+        <v>45</v>
+      </c>
+      <c r="R17" s="15">
+        <f t="shared" si="2"/>
+        <v>0.99460407392418704</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O18" s="13">
+        <v>16</v>
+      </c>
+      <c r="P18" s="15">
+        <f t="shared" si="1"/>
+        <v>5.3959260758127611E-3</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>40</v>
+      </c>
+      <c r="R18" s="12">
+        <f t="shared" si="2"/>
+        <v>0.99999999999999978</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12">
+        <f>SUM(Q3:Q18)</f>
+        <v>7413</v>
+      </c>
+      <c r="R19" s="12"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="P3:Q18">
+    <sortCondition descending="1" ref="Q3:Q18"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DBEF6AD-EAF3-4569-983E-648C49A57002}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" customWidth="1"/>
+    <col min="8" max="8" width="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>12</v>
+      </c>
+      <c r="B2" s="5">
+        <f>((A2-$E$6)/($E$7))^3</f>
+        <v>-4.1725379670486955</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <v>13</v>
+      </c>
+      <c r="B3" s="5">
+        <f t="shared" ref="B3:B21" si="0">((A3-$E$6)/($E$7))^3</f>
+        <v>-3.5885168072613807</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>17</v>
+      </c>
+      <c r="B4" s="5">
+        <f t="shared" si="0"/>
+        <v>-1.7950310172092956</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>21</v>
+      </c>
+      <c r="B5" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.72815585986126108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>24</v>
+      </c>
+      <c r="B6" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.29130480820225985</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="5">
+        <f>AVERAGE(A2:A21)</f>
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>24</v>
+      </c>
+      <c r="B7" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.29130480820225985</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="18">
+        <f>_xlfn.STDEV.S(A2:A21)</f>
+        <v>12.671559535141345</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>26</v>
+      </c>
+      <c r="B8" s="5">
+        <f t="shared" si="0"/>
+        <v>-0.12883970353055349</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="5">
+        <f>COUNT(A2:A21)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <v>27</v>
+      </c>
+      <c r="B9" s="5">
+        <f t="shared" si="0"/>
+        <v>-7.7391109759273796E-2</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>27</v>
+      </c>
+      <c r="B10" s="5">
+        <f t="shared" si="0"/>
+        <v>-7.7391109759273796E-2</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="5">
+        <f>SUM(B2:B21)</f>
+        <v>4.4291400401630501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>30</v>
+      </c>
+      <c r="B11" s="5">
+        <f t="shared" si="0"/>
+        <v>-6.7942812408690262E-3</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>32</v>
+      </c>
+      <c r="B12" s="5">
+        <f t="shared" si="0"/>
+        <v>-3.1455005744763731E-5</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>35</v>
+      </c>
+      <c r="B13" s="5">
+        <f t="shared" si="0"/>
+        <v>8.6383309526558462E-3</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="5">
+        <f>MIN(A2:A21)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5">
+        <f t="shared" si="0"/>
+        <v>4.7839131862068084E-2</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="5">
+        <f xml:space="preserve"> MAX(A2:A21)</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5">
+        <f t="shared" si="0"/>
+        <v>8.6312535763632625E-2</v>
+      </c>
+      <c r="D15" s="5">
+        <v>20</v>
+      </c>
+      <c r="E15" s="5" cm="1">
+        <f t="array" ref="E15:E19">FREQUENCY(A:A,D15:D18)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <v>41</v>
+      </c>
+      <c r="B16" s="5">
+        <f t="shared" si="0"/>
+        <v>0.31261164271861963</v>
+      </c>
+      <c r="D16" s="5">
+        <v>30</v>
+      </c>
+      <c r="E16" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <v>43</v>
+      </c>
+      <c r="B17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.58536586128290513</v>
+      </c>
+      <c r="D17" s="5">
+        <v>40</v>
+      </c>
+      <c r="E17" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>44</v>
+      </c>
+      <c r="B18" s="5">
+        <f t="shared" si="0"/>
+        <v>0.7671561351090509</v>
+      </c>
+      <c r="D18" s="5">
+        <v>50</v>
+      </c>
+      <c r="E18" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <v>46</v>
+      </c>
+      <c r="B19" s="5">
+        <f t="shared" si="0"/>
+        <v>1.2363075457922075</v>
+      </c>
+      <c r="D19" s="5">
+        <v>60</v>
+      </c>
+      <c r="E19" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <v>53</v>
+      </c>
+      <c r="B20" s="5">
+        <f t="shared" si="0"/>
+        <v>4.2964667578073499</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>58</v>
+      </c>
+      <c r="B21" s="5">
+        <f t="shared" si="0"/>
+        <v>8.2457410259554287</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>